--- a/roadmap_2026Q3.xlsx
+++ b/roadmap_2026Q3.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="12">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,6 +61,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
       <sz val="9"/>
     </font>
     <font>
@@ -71,8 +76,12 @@
       <color rgb="00E53935"/>
       <sz val="9"/>
     </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -111,6 +120,21 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2D1F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FBEAB6"/>
       </patternFill>
     </fill>
@@ -120,7 +144,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -256,15 +280,130 @@
         <color rgb="005B9BD5"/>
       </bottom>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="thin">
+        <color rgb="005B9BD5"/>
+      </right>
+      <top style="thin">
+        <color rgb="005B9BD5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="005B9BD5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C77F00"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C77F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C77F00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="medium">
+        <color rgb="002E7D32"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C77F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C77F00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="002F5597"/>
+      </left>
+      <right style="medium">
+        <color rgb="002E7D32"/>
+      </right>
+      <top style="thin">
+        <color rgb="005B9BD5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="005B9BD5"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D9D9D9"/>
+      </left>
+      <right style="medium">
+        <color rgb="007F0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D9D9D9"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00C77F00"/>
+      </left>
+      <right style="medium">
+        <color rgb="007F0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C77F00"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00C77F00"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="005B9BD5"/>
+      </left>
+      <right style="medium">
+        <color rgb="007F0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="005B9BD5"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="005B9BD5"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -273,42 +412,71 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -674,7 +842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:Q67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -730,1643 +898,1666 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="30" customHeight="1">
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>22-28</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
+          <t>⚑ Старт
+22-28</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>29-05</t>
         </is>
       </c>
-      <c r="E3" s="4" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>06-12</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>13-19</t>
         </is>
       </c>
-      <c r="G3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>20-26</t>
         </is>
       </c>
-      <c r="H3" s="4" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>27-02</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
         <is>
           <t>03-09</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>10-16</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>17-23</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>24-30</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>31-06</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>07-13</t>
         </is>
       </c>
-      <c r="O3" s="4" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>14-20</t>
         </is>
       </c>
-      <c r="P3" s="4" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>21-27</t>
         </is>
       </c>
-      <c r="Q3" s="4" t="inlineStr">
-        <is>
-          <t>28-04</t>
+      <c r="Q3" s="7" t="inlineStr">
+        <is>
+          <t>⚑ Финиш
+28-04</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5286 Форма хронологии контрагента (периметр КГ)
 (Дима (SDD); Максим, Таня (dev))
 Сервисы: БФФ, Байкал5, ЕПК, ЦПС</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): периметр КГ</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 22.06</t>
         </is>
       </c>
-      <c r="D4" s="9" t="n"/>
-      <c r="E4" s="9" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="9" t="n"/>
-      <c r="H4" s="9" t="n"/>
-      <c r="I4" s="9" t="n"/>
-      <c r="J4" s="9" t="n"/>
-      <c r="K4" s="9" t="n"/>
-      <c r="L4" s="9" t="n"/>
-      <c r="M4" s="9" t="n"/>
-      <c r="N4" s="9" t="n"/>
-      <c r="O4" s="9" t="n"/>
-      <c r="P4" s="9" t="n"/>
-      <c r="Q4" s="9" t="n"/>
+      <c r="D4" s="11" t="n"/>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="12" t="n"/>
+      <c r="G4" s="11" t="n"/>
+      <c r="H4" s="11" t="n"/>
+      <c r="I4" s="11" t="n"/>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="11" t="n"/>
+      <c r="M4" s="11" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="O4" s="11" t="n"/>
+      <c r="P4" s="11" t="n"/>
+      <c r="Q4" s="12" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="11" t="n"/>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="A5" s="13" t="n"/>
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Таня (UI): BFF Периметр КГ, виджет</t>
         </is>
       </c>
-      <c r="C5" s="12" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>BFF Периметр КГ.PL</t>
         </is>
       </c>
-      <c r="D5" s="13" t="n"/>
-      <c r="E5" s="13" t="n"/>
-      <c r="F5" s="10" t="n"/>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="9" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="12" t="n"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="11" t="n"/>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="11" t="n"/>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="O5" s="11" t="n"/>
+      <c r="P5" s="11" t="n"/>
+      <c r="Q5" s="12" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="n"/>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="A6" s="13" t="n"/>
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Максим: запрос в БФФ (Байкал5), обогащение из ЕПК</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="9" t="n"/>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="C6" s="16" t="n"/>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="17" t="inlineStr">
         <is>
           <t>Байкал, ЕПК ◇ финиш 19.07</t>
         </is>
       </c>
-      <c r="F6" s="13" t="n"/>
-      <c r="G6" s="9" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="9" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="9" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="11" t="n"/>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="O6" s="11" t="n"/>
+      <c r="P6" s="11" t="n"/>
+      <c r="Q6" s="12" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5499 Внедрение агентов ФЖН
 (Егор (SDD); АЕФ, Даша, Таня (dev))
 Сервисы: ЦПС, БФФ, РА, ЭКД</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Егор): Агент ФЖН [SDD]</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 22.06</t>
         </is>
       </c>
-      <c r="D7" s="15" t="n"/>
-      <c r="E7" s="9" t="n"/>
-      <c r="F7" s="16" t="inlineStr">
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="19" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="9" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n"/>
+      <c r="I7" s="12" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="O7" s="11" t="n"/>
+      <c r="P7" s="11" t="n"/>
+      <c r="Q7" s="12" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="11" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>АЕФ: внедрение агентов [SDD], 50 чд</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>АЕФ.суммаризатор</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n"/>
-      <c r="E8" s="13" t="n"/>
-      <c r="F8" s="13" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="9" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="O8" s="11" t="n"/>
+      <c r="P8" s="11" t="n"/>
+      <c r="Q8" s="12" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="11" t="n"/>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Даша: агент ФЖН в ЦПС (БФФ→РА→ЭКД, риск-метрики)</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="12" t="inlineStr">
+      <c r="C9" s="16" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t>Агент ФЖН.Checklist-verif. 13чд</t>
         </is>
       </c>
-      <c r="G9" s="13" t="n"/>
-      <c r="H9" s="13" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="O9" s="11" t="n"/>
+      <c r="P9" s="11" t="n"/>
+      <c r="Q9" s="12" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Таня (UI): новый микрофронт + поллинг (3+3 чд)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="9" t="n"/>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="11" t="n"/>
+      <c r="H10" s="17" t="inlineStr">
         <is>
           <t>ЦПС.микрофронт.PL ◇ финиш 09.08</t>
         </is>
       </c>
-      <c r="I10" s="13" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="9" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
-      <c r="O10" s="9" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="11" t="n"/>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="O10" s="11" t="n"/>
+      <c r="P10" s="11" t="n"/>
+      <c r="Q10" s="12" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5694 НЭР: предконтроль по рискам (СберФакторинг)
 (Юля (SDD); Мурад, Антон, Миша, Эрнест (dev))
 Сервисы: НЭР, РЭКИБ</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Юля): предконтроль по рискам СберФакторинг [SDD]</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="8" t="inlineStr">
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 29.06</t>
         </is>
       </c>
-      <c r="E11" s="15" t="n"/>
-      <c r="F11" s="15" t="n"/>
-      <c r="G11" s="15" t="n"/>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="15" t="n"/>
-      <c r="J11" s="15" t="n"/>
-      <c r="K11" s="9" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="18" t="n"/>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="12" t="n"/>
+      <c r="O11" s="11" t="n"/>
+      <c r="P11" s="11" t="n"/>
+      <c r="Q11" s="12" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Миша: УЗ — настроечная таблица (2 чд)</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="10" t="n"/>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="21" t="inlineStr">
         <is>
           <t>РЭКИБ.УЗ.doc-processor</t>
         </is>
       </c>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="9" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="11" t="n"/>
+      <c r="P12" s="11" t="n"/>
+      <c r="Q12" s="12" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Мурад: РЭКИБ РА (result-app, handler-app, handler-risk-app) — АПИ + БД</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-      <c r="E13" s="9" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="12" t="inlineStr">
+      <c r="C13" s="16" t="n"/>
+      <c r="D13" s="16" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="22" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="21" t="inlineStr">
         <is>
           <t>РЭКИБ.РА.result-app</t>
         </is>
       </c>
-      <c r="L13" s="13" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="11" t="n"/>
+      <c r="P13" s="11" t="n"/>
+      <c r="Q13" s="12" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Антон: РЭКИБ КП (result-app, handler-app, handler-risk-app), 15 чд</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="9" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="12" t="inlineStr">
+      <c r="C14" s="16" t="n"/>
+      <c r="D14" s="16" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="22" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="17" t="inlineStr">
         <is>
           <t>РЭКИБ.КП.result-app</t>
         </is>
       </c>
-      <c r="L14" s="13" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="11" t="n"/>
+      <c r="P14" s="11" t="n"/>
+      <c r="Q14" s="12" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>Эрнест (UI): УЗ — виджет от КП (5 чд)</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="12" t="inlineStr">
+      <c r="C15" s="16" t="n"/>
+      <c r="D15" s="16" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="21" t="inlineStr">
         <is>
           <t>НЭР.виджет.PL (КП)</t>
         </is>
       </c>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="17" t="inlineStr">
+      <c r="L15" s="11" t="n"/>
+      <c r="M15" s="11" t="n"/>
+      <c r="N15" s="23" t="inlineStr">
         <is>
           <t>◇ финиш 13.09</t>
         </is>
       </c>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
+      <c r="O15" s="11" t="n"/>
+      <c r="P15" s="11" t="n"/>
+      <c r="Q15" s="12" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5695 НЭР: предконтроль модели CF
 (Дима (SDD); Гоша (dev))
 Сервисы: НЭР, ЭКД</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): предконтроль модели CF перед отправкой на НЭР</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="9" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="9" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="C16" s="16" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="22" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 03.08</t>
         </is>
       </c>
-      <c r="J16" s="15" t="n"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
-      <c r="O16" s="9" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="11" t="n"/>
+      <c r="L16" s="11" t="n"/>
+      <c r="M16" s="11" t="n"/>
+      <c r="N16" s="11" t="n"/>
+      <c r="O16" s="12" t="n"/>
+      <c r="P16" s="11" t="n"/>
+      <c r="Q16" s="12" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="11" t="n"/>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>Гоша: РЭКИБ РА (result-app, handler-app, handler-risk-app) — интеграция, сценарий ЧЛ в ЭКД, 10 чд</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="9" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="12" t="inlineStr">
+      <c r="C17" s="16" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="22" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="16" t="n"/>
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="11" t="n"/>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>РЭКИБ.РА.result-app ◇ финиш 20.09</t>
         </is>
       </c>
-      <c r="M17" s="13" t="n"/>
-      <c r="N17" s="13" t="n"/>
-      <c r="O17" s="13" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="11" t="n"/>
+      <c r="Q17" s="12" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5697 НЭР: внешние сервисы, принятие решения 26Q3
 (Дима, Настя, Егор (SDD); Максим (dev))
 Сервисы: НЭР, УФА, ЕФС, ОКК, БКИ, РЭКИБ.ЦПС</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Настя): ОКК (OCRED-25995)</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="9" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="8" t="inlineStr">
+      <c r="C18" s="16" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 20.07</t>
         </is>
       </c>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
-      <c r="O18" s="9" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="11" t="n"/>
+      <c r="L18" s="11" t="n"/>
+      <c r="M18" s="11" t="n"/>
+      <c r="N18" s="11" t="n"/>
+      <c r="O18" s="12" t="n"/>
+      <c r="P18" s="11" t="n"/>
+      <c r="Q18" s="12" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11" t="n"/>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): Топик МД</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="8" t="inlineStr">
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="22" t="n"/>
+      <c r="G19" s="16" t="n"/>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
+      <c r="I19" s="11" t="n"/>
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="11" t="n"/>
+      <c r="L19" s="11" t="n"/>
+      <c r="M19" s="11" t="n"/>
+      <c r="N19" s="11" t="n"/>
+      <c r="O19" s="12" t="n"/>
+      <c r="P19" s="11" t="n"/>
+      <c r="Q19" s="12" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Егор): Профиль сотрудника</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="9" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="9" t="n"/>
-      <c r="H20" s="8" t="inlineStr">
+      <c r="C20" s="16" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="22" t="n"/>
+      <c r="G20" s="16" t="n"/>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="I20" s="15" t="n"/>
-      <c r="J20" s="15" t="n"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
-      <c r="O20" s="9" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="11" t="n"/>
+      <c r="L20" s="11" t="n"/>
+      <c r="M20" s="11" t="n"/>
+      <c r="N20" s="11" t="n"/>
+      <c r="O20" s="12" t="n"/>
+      <c r="P20" s="11" t="n"/>
+      <c r="Q20" s="12" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Егор): УФА (РА/Заключение), БКИ (РА)</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="8" t="inlineStr">
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="22" t="n"/>
+      <c r="G21" s="16" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
+      <c r="L21" s="11" t="n"/>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="O21" s="12" t="n"/>
+      <c r="P21" s="11" t="n"/>
+      <c r="Q21" s="12" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="11" t="n"/>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Егор): БКИ (КП)</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="9" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="8" t="inlineStr">
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="22" t="n"/>
+      <c r="G22" s="16" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="9" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="O22" s="12" t="n"/>
+      <c r="P22" s="11" t="n"/>
+      <c r="Q22" s="12" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="11" t="n"/>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>Максим: код ОКК по мониторингу клиента (3 ч/д)</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="12" t="inlineStr">
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="14" t="inlineStr">
         <is>
           <t>ОКК</t>
         </is>
       </c>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="11" t="n"/>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="O23" s="12" t="n"/>
+      <c r="P23" s="11" t="n"/>
+      <c r="Q23" s="12" t="n"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="11" t="n"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>Максим: фин. анализ УФА, +2 интеграции, маппинги (20 чд)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-      <c r="E24" s="9" t="n"/>
-      <c r="F24" s="10" t="n"/>
-      <c r="G24" s="9" t="n"/>
-      <c r="H24" s="9" t="n"/>
-      <c r="I24" s="9" t="n"/>
-      <c r="J24" s="12" t="inlineStr">
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="22" t="n"/>
+      <c r="G24" s="16" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>НЭР.УФА</t>
         </is>
       </c>
-      <c r="K24" s="13" t="n"/>
-      <c r="L24" s="13" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="9" t="n"/>
-      <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="O24" s="12" t="n"/>
+      <c r="P24" s="11" t="n"/>
+      <c r="Q24" s="12" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="11" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>Максим: ЕФС.ПР — переход на search/getProfile (3 ч/д)</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
-      <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="12" t="inlineStr">
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="22" t="n"/>
+      <c r="G25" s="16" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="21" t="inlineStr">
         <is>
           <t>ЕФС.ПР</t>
         </is>
       </c>
-      <c r="O25" s="9" t="n"/>
-      <c r="P25" s="9" t="n"/>
-      <c r="Q25" s="9" t="n"/>
+      <c r="O25" s="12" t="n"/>
+      <c r="P25" s="11" t="n"/>
+      <c r="Q25" s="12" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="11" t="n"/>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>Максим: РЭКИБ.ЦПС — проверка использования search (3 ч/д)</t>
         </is>
       </c>
-      <c r="C26" s="9" t="n"/>
-      <c r="D26" s="9" t="n"/>
-      <c r="E26" s="9" t="n"/>
-      <c r="F26" s="10" t="n"/>
-      <c r="G26" s="9" t="n"/>
-      <c r="H26" s="9" t="n"/>
-      <c r="I26" s="9" t="n"/>
-      <c r="J26" s="9" t="n"/>
-      <c r="K26" s="9" t="n"/>
-      <c r="L26" s="9" t="n"/>
-      <c r="M26" s="9" t="n"/>
-      <c r="N26" s="9" t="n"/>
-      <c r="O26" s="12" t="inlineStr">
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="22" t="n"/>
+      <c r="G26" s="16" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="11" t="n"/>
+      <c r="O26" s="17" t="inlineStr">
         <is>
           <t>РЭКИБ.ЦПС.supplier ◇ финиш 20.09</t>
         </is>
       </c>
-      <c r="P26" s="9" t="n"/>
-      <c r="Q26" s="9" t="n"/>
+      <c r="P26" s="11" t="n"/>
+      <c r="Q26" s="12" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5698 НЭР: подключение ESG
 (Настя (SDD); Антон, Гоша, Эрнест (dev))
 Сервисы: НЭР, РЭКИБ, ЕФС</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Настя): подключение ESG [SDD]</t>
         </is>
       </c>
-      <c r="C27" s="16" t="inlineStr">
+      <c r="C27" s="25" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 22.06</t>
         </is>
       </c>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-      <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n"/>
-      <c r="K27" s="9" t="n"/>
-      <c r="L27" s="9" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
-      <c r="Q27" s="9" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="11" t="n"/>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="O27" s="11" t="n"/>
+      <c r="P27" s="11" t="n"/>
+      <c r="Q27" s="12" t="n"/>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>Антон: РЭКИБ КП (result-app, handler-app, handler-risk-app) — метрики, справочники, маппинг</t>
         </is>
       </c>
-      <c r="C28" s="9" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>РЭКИБ.КП.result-app / ЕФС.КП.BFF</t>
         </is>
       </c>
-      <c r="F28" s="13" t="n"/>
-      <c r="G28" s="13" t="n"/>
-      <c r="H28" s="9" t="n"/>
-      <c r="I28" s="9" t="n"/>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
-      <c r="L28" s="9" t="n"/>
-      <c r="M28" s="9" t="n"/>
-      <c r="N28" s="9" t="n"/>
-      <c r="O28" s="9" t="n"/>
-      <c r="P28" s="9" t="n"/>
-      <c r="Q28" s="9" t="n"/>
+      <c r="F28" s="15" t="n"/>
+      <c r="G28" s="15" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="11" t="n"/>
+      <c r="O28" s="11" t="n"/>
+      <c r="P28" s="11" t="n"/>
+      <c r="Q28" s="12" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>Гоша: РЭКИБ РА (result-app, handler-app, handler-risk-app) — новая стратегия, 10 чд</t>
         </is>
       </c>
-      <c r="C29" s="9" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="9" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="12" t="inlineStr">
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="22" t="n"/>
+      <c r="G29" s="17" t="inlineStr">
         <is>
           <t>РЭКИБ.РА.result-app</t>
         </is>
       </c>
-      <c r="H29" s="13" t="n"/>
-      <c r="I29" s="13" t="n"/>
-      <c r="J29" s="13" t="n"/>
-      <c r="K29" s="9" t="n"/>
-      <c r="L29" s="9" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="9" t="n"/>
-      <c r="P29" s="9" t="n"/>
-      <c r="Q29" s="9" t="n"/>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="15" t="n"/>
+      <c r="J29" s="15" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="O29" s="11" t="n"/>
+      <c r="P29" s="11" t="n"/>
+      <c r="Q29" s="12" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11" t="n"/>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Эрнест (UI): подключение ESG (5 чд)</t>
         </is>
       </c>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="9" t="n"/>
-      <c r="F30" s="10" t="n"/>
-      <c r="G30" s="9" t="n"/>
-      <c r="H30" s="12" t="inlineStr">
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="22" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="21" t="inlineStr">
         <is>
           <t>НЭР.UI.PL (ESG)</t>
         </is>
       </c>
-      <c r="I30" s="13" t="n"/>
-      <c r="J30" s="17" t="inlineStr">
+      <c r="I30" s="15" t="n"/>
+      <c r="J30" s="23" t="inlineStr">
         <is>
           <t>◇ финиш 16.08</t>
         </is>
       </c>
-      <c r="K30" s="9" t="n"/>
-      <c r="L30" s="9" t="n"/>
-      <c r="M30" s="9" t="n"/>
-      <c r="N30" s="9" t="n"/>
-      <c r="O30" s="9" t="n"/>
-      <c r="P30" s="9" t="n"/>
-      <c r="Q30" s="9" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="11" t="n"/>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="O30" s="11" t="n"/>
+      <c r="P30" s="11" t="n"/>
+      <c r="Q30" s="12" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5699 РА: агент по хронологии
 (Дима (SDD); Рим, Даша, Таня, АЕФ (dev))
 Сервисы: ЦПС, БФФ, ЕПК, AI-Hub</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): Агент Хронологии (без Риск-ассистента)</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>◆ старт 22.06</t>
         </is>
       </c>
-      <c r="D31" s="8" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="22" t="n"/>
+      <c r="G31" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="n"/>
-      <c r="L31" s="9" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
-      <c r="Q31" s="9" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="O31" s="11" t="n"/>
+      <c r="P31" s="11" t="n"/>
+      <c r="Q31" s="12" t="n"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>Рим: хронология-БФФ, отдельный микросервис в ЦПС (10 чд)</t>
         </is>
       </c>
-      <c r="C32" s="12" t="inlineStr">
+      <c r="C32" s="14" t="inlineStr">
         <is>
           <t>ЦПС.хронология.BFF</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="n"/>
-      <c r="L32" s="9" t="n"/>
-      <c r="M32" s="9" t="n"/>
-      <c r="N32" s="9" t="n"/>
-      <c r="O32" s="9" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
+      <c r="D32" s="15" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="22" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="11" t="n"/>
+      <c r="L32" s="11" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="11" t="n"/>
+      <c r="O32" s="11" t="n"/>
+      <c r="P32" s="11" t="n"/>
+      <c r="Q32" s="12" t="n"/>
     </row>
     <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="11" t="n"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>АЕФ: 45 чд (оценка под вопросом)</t>
         </is>
       </c>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="10" t="n"/>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="22" t="n"/>
+      <c r="G33" s="17" t="inlineStr">
         <is>
           <t>АЕФ 45 чд ?</t>
         </is>
       </c>
-      <c r="H33" s="13" t="n"/>
-      <c r="I33" s="13" t="n"/>
-      <c r="J33" s="13" t="n"/>
-      <c r="K33" s="13" t="n"/>
-      <c r="L33" s="13" t="n"/>
-      <c r="M33" s="13" t="n"/>
-      <c r="N33" s="9" t="n"/>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
-      <c r="Q33" s="9" t="n"/>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="15" t="n"/>
+      <c r="J33" s="15" t="n"/>
+      <c r="K33" s="15" t="n"/>
+      <c r="L33" s="15" t="n"/>
+      <c r="M33" s="15" t="n"/>
+      <c r="N33" s="11" t="n"/>
+      <c r="O33" s="11" t="n"/>
+      <c r="P33" s="11" t="n"/>
+      <c r="Q33" s="12" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>Даша: ЕПК_id от UI → запрос в AI-Hub (5 чд)</t>
         </is>
       </c>
-      <c r="C34" s="9" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="9" t="n"/>
-      <c r="F34" s="10" t="n"/>
-      <c r="G34" s="9" t="n"/>
-      <c r="H34" s="9" t="n"/>
-      <c r="I34" s="12" t="inlineStr">
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="22" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="21" t="inlineStr">
         <is>
           <t>РЭКИБ.РА.handler-app (AI-Hub)</t>
         </is>
       </c>
-      <c r="J34" s="13" t="n"/>
-      <c r="K34" s="9" t="n"/>
-      <c r="L34" s="9" t="n"/>
-      <c r="M34" s="9" t="n"/>
-      <c r="N34" s="9" t="n"/>
-      <c r="O34" s="9" t="n"/>
-      <c r="P34" s="9" t="n"/>
-      <c r="Q34" s="9" t="n"/>
+      <c r="J34" s="15" t="n"/>
+      <c r="K34" s="11" t="n"/>
+      <c r="L34" s="11" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="11" t="n"/>
+      <c r="O34" s="11" t="n"/>
+      <c r="P34" s="11" t="n"/>
+      <c r="Q34" s="12" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>Таня (UI): виджет «Хронология», плашки негативных событий (10 чд)</t>
         </is>
       </c>
-      <c r="C35" s="9" t="n"/>
-      <c r="D35" s="9" t="n"/>
-      <c r="E35" s="9" t="n"/>
-      <c r="F35" s="10" t="n"/>
-      <c r="G35" s="9" t="n"/>
-      <c r="H35" s="9" t="n"/>
-      <c r="I35" s="9" t="n"/>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="22" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
+      <c r="J35" s="17" t="inlineStr">
         <is>
           <t>ЦПС.виджет.PL «Хронология» ◇ финиш 06.09</t>
         </is>
       </c>
-      <c r="K35" s="13" t="n"/>
-      <c r="L35" s="13" t="n"/>
-      <c r="M35" s="13" t="n"/>
-      <c r="N35" s="9" t="n"/>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
-      <c r="Q35" s="9" t="n"/>
+      <c r="K35" s="15" t="n"/>
+      <c r="L35" s="15" t="n"/>
+      <c r="M35" s="15" t="n"/>
+      <c r="N35" s="11" t="n"/>
+      <c r="O35" s="11" t="n"/>
+      <c r="P35" s="11" t="n"/>
+      <c r="Q35" s="12" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5715 ККА: интеграция с СУДИР (отказ от SOAP)
 (Ульяна (SDD); Мурад (dev))
 Сервисы: ККА, СУДИР</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Ульяна): ККА интеграция с СУДИР, 10 чд [SDD]</t>
         </is>
       </c>
-      <c r="C36" s="8" t="inlineStr">
+      <c r="C36" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 22.06</t>
         </is>
       </c>
-      <c r="D36" s="15" t="n"/>
-      <c r="E36" s="9" t="n"/>
-      <c r="F36" s="10" t="n"/>
-      <c r="G36" s="9" t="n"/>
-      <c r="H36" s="9" t="n"/>
-      <c r="I36" s="9" t="n"/>
-      <c r="J36" s="9" t="n"/>
-      <c r="K36" s="9" t="n"/>
-      <c r="L36" s="9" t="n"/>
-      <c r="M36" s="9" t="n"/>
-      <c r="N36" s="9" t="n"/>
-      <c r="O36" s="9" t="n"/>
-      <c r="P36" s="9" t="n"/>
-      <c r="Q36" s="9" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="11" t="n"/>
+      <c r="L36" s="11" t="n"/>
+      <c r="M36" s="11" t="n"/>
+      <c r="N36" s="11" t="n"/>
+      <c r="O36" s="11" t="n"/>
+      <c r="P36" s="11" t="n"/>
+      <c r="Q36" s="12" t="n"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="11" t="n"/>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>Мурад: интеграция (20 чд)</t>
         </is>
       </c>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="10" t="n"/>
-      <c r="G37" s="12" t="inlineStr">
+      <c r="C37" s="16" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="22" t="n"/>
+      <c r="G37" s="17" t="inlineStr">
         <is>
           <t>ККА.handler-app (СУДИР/REST) ◇ финиш 16.08</t>
         </is>
       </c>
-      <c r="H37" s="13" t="n"/>
-      <c r="I37" s="13" t="n"/>
-      <c r="J37" s="13" t="n"/>
-      <c r="K37" s="9" t="n"/>
-      <c r="L37" s="9" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="9" t="n"/>
-      <c r="P37" s="9" t="n"/>
-      <c r="Q37" s="9" t="n"/>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="15" t="n"/>
+      <c r="J37" s="15" t="n"/>
+      <c r="K37" s="11" t="n"/>
+      <c r="L37" s="11" t="n"/>
+      <c r="M37" s="11" t="n"/>
+      <c r="N37" s="11" t="n"/>
+      <c r="O37" s="11" t="n"/>
+      <c r="P37" s="11" t="n"/>
+      <c r="Q37" s="12" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>ARGUSRA-5724 ЦКП [BEST OFFERS 4.0]
 (Настя, Юля (SDD); Рим, Даша, Таня, Эрнест (dev))
 Сервисы: ЦКП, ЦПС, ОКК, РМКИ</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Настя): Лимиты ОФР в ЦКП (ветка с откл. / МВП)</t>
         </is>
       </c>
-      <c r="C38" s="9" t="n"/>
-      <c r="D38" s="9" t="n"/>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="10" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="8" t="inlineStr">
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="22" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>аналитика ◆ старт 10.08</t>
         </is>
       </c>
-      <c r="K38" s="15" t="n"/>
-      <c r="L38" s="9" t="n"/>
-      <c r="M38" s="9" t="n"/>
-      <c r="N38" s="9" t="n"/>
-      <c r="O38" s="9" t="n"/>
-      <c r="P38" s="9" t="n"/>
-      <c r="Q38" s="9" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="11" t="n"/>
+      <c r="M38" s="11" t="n"/>
+      <c r="N38" s="11" t="n"/>
+      <c r="O38" s="12" t="n"/>
+      <c r="P38" s="11" t="n"/>
+      <c r="Q38" s="12" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="11" t="n"/>
-      <c r="B39" s="7" t="inlineStr">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Настя): BEST OFFERS 4.0 — внедрение в ЦКП: ЦПС</t>
         </is>
       </c>
-      <c r="C39" s="9" t="n"/>
-      <c r="D39" s="9" t="n"/>
-      <c r="E39" s="9" t="n"/>
-      <c r="F39" s="10" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
-      <c r="L39" s="8" t="inlineStr">
+      <c r="C39" s="16" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="22" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
+      <c r="J39" s="16" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="M39" s="15" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
-      <c r="Q39" s="9" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="O39" s="12" t="n"/>
+      <c r="P39" s="11" t="n"/>
+      <c r="Q39" s="12" t="n"/>
     </row>
     <row r="40" ht="22" customHeight="1">
-      <c r="A40" s="11" t="n"/>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Юля): презентация по сделкам ПРПА</t>
         </is>
       </c>
-      <c r="C40" s="9" t="n"/>
-      <c r="D40" s="9" t="n"/>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="n"/>
-      <c r="L40" s="9" t="n"/>
-      <c r="M40" s="8" t="inlineStr">
+      <c r="C40" s="16" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="22" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="16" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="11" t="n"/>
+      <c r="M40" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="N40" s="15" t="n"/>
-      <c r="O40" s="9" t="n"/>
-      <c r="P40" s="9" t="n"/>
-      <c r="Q40" s="9" t="n"/>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="12" t="n"/>
+      <c r="P40" s="11" t="n"/>
+      <c r="Q40" s="12" t="n"/>
     </row>
     <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="11" t="n"/>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="9" t="inlineStr">
         <is>
           <t>Рим: ЦПС А, ОКК, суммаризация рисков, ПРПА, Сделки_ДЗО</t>
         </is>
       </c>
-      <c r="C41" s="9" t="n"/>
-      <c r="D41" s="9" t="n"/>
-      <c r="E41" s="9" t="n"/>
-      <c r="F41" s="10" t="n"/>
-      <c r="G41" s="9" t="n"/>
-      <c r="H41" s="9" t="n"/>
-      <c r="I41" s="9" t="n"/>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
-      <c r="L41" s="12" t="inlineStr">
+      <c r="C41" s="16" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="22" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
+      <c r="J41" s="16" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="21" t="inlineStr">
         <is>
           <t>ЦКП.ЦПС.result-app</t>
         </is>
       </c>
-      <c r="M41" s="13" t="n"/>
-      <c r="N41" s="13" t="n"/>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
-      <c r="Q41" s="9" t="n"/>
+      <c r="M41" s="15" t="n"/>
+      <c r="N41" s="15" t="n"/>
+      <c r="O41" s="12" t="n"/>
+      <c r="P41" s="11" t="n"/>
+      <c r="Q41" s="12" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="11" t="n"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>Даша: ЦПС А, ОКК, суммаризация рисков, ПРПА, Сделки_ДЗО</t>
         </is>
       </c>
-      <c r="C42" s="9" t="n"/>
-      <c r="D42" s="9" t="n"/>
-      <c r="E42" s="9" t="n"/>
-      <c r="F42" s="10" t="n"/>
-      <c r="G42" s="9" t="n"/>
-      <c r="H42" s="9" t="n"/>
-      <c r="I42" s="9" t="n"/>
-      <c r="J42" s="9" t="n"/>
-      <c r="K42" s="9" t="n"/>
-      <c r="L42" s="12" t="inlineStr">
+      <c r="C42" s="16" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="22" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="16" t="n"/>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="21" t="inlineStr">
         <is>
           <t>Риски.РА.result-app</t>
         </is>
       </c>
-      <c r="M42" s="13" t="n"/>
-      <c r="N42" s="13" t="n"/>
-      <c r="O42" s="9" t="n"/>
-      <c r="P42" s="9" t="n"/>
-      <c r="Q42" s="9" t="n"/>
+      <c r="M42" s="15" t="n"/>
+      <c r="N42" s="15" t="n"/>
+      <c r="O42" s="12" t="n"/>
+      <c r="P42" s="11" t="n"/>
+      <c r="Q42" s="12" t="n"/>
     </row>
     <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="11" t="n"/>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>Таня (UI): фронт — ЦПС А, УЗ, Риски/РА, РМКИ-лизинг</t>
         </is>
       </c>
-      <c r="C43" s="9" t="n"/>
-      <c r="D43" s="9" t="n"/>
-      <c r="E43" s="9" t="n"/>
-      <c r="F43" s="10" t="n"/>
-      <c r="G43" s="9" t="n"/>
-      <c r="H43" s="9" t="n"/>
-      <c r="I43" s="9" t="n"/>
-      <c r="J43" s="9" t="n"/>
-      <c r="K43" s="9" t="n"/>
-      <c r="L43" s="9" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="12" t="inlineStr">
+      <c r="C43" s="16" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="22" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="16" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="17" t="inlineStr">
         <is>
           <t>ЦКП.фронт.PL (ЦПС)</t>
         </is>
       </c>
-      <c r="O43" s="13" t="n"/>
-      <c r="P43" s="9" t="n"/>
-      <c r="Q43" s="9" t="n"/>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="11" t="n"/>
+      <c r="Q43" s="12" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="11" t="n"/>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>Эрнест (UI): фронт — ЦПС А, УЗ, Риски/РА, РМКИ-лизинг</t>
         </is>
       </c>
-      <c r="C44" s="9" t="n"/>
-      <c r="D44" s="9" t="n"/>
-      <c r="E44" s="9" t="n"/>
-      <c r="F44" s="10" t="n"/>
-      <c r="G44" s="9" t="n"/>
-      <c r="H44" s="9" t="n"/>
-      <c r="I44" s="9" t="n"/>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
-      <c r="L44" s="9" t="n"/>
-      <c r="M44" s="9" t="n"/>
-      <c r="N44" s="12" t="inlineStr">
+      <c r="C44" s="16" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="22" t="n"/>
+      <c r="G44" s="11" t="n"/>
+      <c r="H44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="16" t="n"/>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="17" t="inlineStr">
         <is>
           <t>ЦКП.фронт.PL (УЗ) ◇ финиш 20.09</t>
         </is>
       </c>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
+      <c r="O44" s="15" t="n"/>
+      <c r="P44" s="11" t="n"/>
+      <c r="Q44" s="12" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>Задачи вне тикетов (аналитика + разработка)</t>
         </is>
       </c>
-      <c r="B45" s="7" t="inlineStr">
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): комплектность перед НРЭ</t>
         </is>
       </c>
-      <c r="C45" s="8" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="10" t="n"/>
-      <c r="G45" s="9" t="n"/>
-      <c r="H45" s="9" t="n"/>
-      <c r="I45" s="9" t="n"/>
-      <c r="J45" s="9" t="n"/>
-      <c r="K45" s="9" t="n"/>
-      <c r="L45" s="9" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
-      <c r="O45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
-      <c r="Q45" s="9" t="n"/>
+      <c r="D45" s="11" t="n"/>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="22" t="n"/>
+      <c r="G45" s="11" t="n"/>
+      <c r="H45" s="11" t="n"/>
+      <c r="I45" s="11" t="n"/>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="11" t="n"/>
+      <c r="M45" s="12" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="O45" s="11" t="n"/>
+      <c r="P45" s="11" t="n"/>
+      <c r="Q45" s="12" t="n"/>
     </row>
     <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="11" t="n"/>
-      <c r="B46" s="7" t="inlineStr">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Дима): Сделки_ДЗО — ПАЛ/ИР, откл. FR/ПБ, КО из РМКИ лизинг</t>
         </is>
       </c>
-      <c r="C46" s="9" t="n"/>
-      <c r="D46" s="9" t="n"/>
-      <c r="E46" s="9" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="9" t="n"/>
-      <c r="H46" s="9" t="n"/>
-      <c r="I46" s="9" t="n"/>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="8" t="inlineStr">
+      <c r="C46" s="16" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="22" t="n"/>
+      <c r="G46" s="11" t="n"/>
+      <c r="H46" s="11" t="n"/>
+      <c r="I46" s="11" t="n"/>
+      <c r="J46" s="11" t="n"/>
+      <c r="K46" s="27" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="L46" s="15" t="n"/>
-      <c r="M46" s="15" t="n"/>
-      <c r="N46" s="9" t="n"/>
-      <c r="O46" s="9" t="n"/>
-      <c r="P46" s="9" t="n"/>
-      <c r="Q46" s="9" t="n"/>
+      <c r="L46" s="18" t="n"/>
+      <c r="M46" s="18" t="n"/>
+      <c r="N46" s="11" t="n"/>
+      <c r="O46" s="11" t="n"/>
+      <c r="P46" s="11" t="n"/>
+      <c r="Q46" s="12" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="11" t="n"/>
-      <c r="B47" s="7" t="inlineStr">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Настя): выход на КО по сделкам СБЛ</t>
         </is>
       </c>
-      <c r="C47" s="9" t="n"/>
-      <c r="D47" s="9" t="n"/>
-      <c r="E47" s="9" t="n"/>
-      <c r="F47" s="10" t="n"/>
-      <c r="G47" s="9" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
+      <c r="C47" s="16" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="22" t="n"/>
+      <c r="G47" s="11" t="n"/>
+      <c r="H47" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="I47" s="9" t="n"/>
-      <c r="J47" s="9" t="n"/>
-      <c r="K47" s="9" t="n"/>
-      <c r="L47" s="9" t="n"/>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="9" t="n"/>
-      <c r="O47" s="9" t="n"/>
-      <c r="P47" s="9" t="n"/>
-      <c r="Q47" s="9" t="n"/>
+      <c r="I47" s="11" t="n"/>
+      <c r="J47" s="11" t="n"/>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="12" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="O47" s="11" t="n"/>
+      <c r="P47" s="11" t="n"/>
+      <c r="Q47" s="12" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="11" t="n"/>
-      <c r="B48" s="7" t="inlineStr">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Юля): доработка новых метрик по фин. риску</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C48" s="10" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="D48" s="9" t="n"/>
-      <c r="E48" s="9" t="n"/>
-      <c r="F48" s="10" t="n"/>
-      <c r="G48" s="9" t="n"/>
-      <c r="H48" s="9" t="n"/>
-      <c r="I48" s="9" t="n"/>
-      <c r="J48" s="9" t="n"/>
-      <c r="K48" s="9" t="n"/>
-      <c r="L48" s="9" t="n"/>
-      <c r="M48" s="9" t="n"/>
-      <c r="N48" s="9" t="n"/>
-      <c r="O48" s="9" t="n"/>
-      <c r="P48" s="9" t="n"/>
-      <c r="Q48" s="9" t="n"/>
+      <c r="D48" s="11" t="n"/>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="22" t="n"/>
+      <c r="G48" s="11" t="n"/>
+      <c r="H48" s="11" t="n"/>
+      <c r="I48" s="11" t="n"/>
+      <c r="J48" s="11" t="n"/>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="11" t="n"/>
+      <c r="M48" s="12" t="n"/>
+      <c r="N48" s="11" t="n"/>
+      <c r="O48" s="11" t="n"/>
+      <c r="P48" s="11" t="n"/>
+      <c r="Q48" s="12" t="n"/>
     </row>
     <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="11" t="n"/>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>Аналитика (Егор): гарант. доставка событий аудита AI Risk HUB; перенос ЦКИ на РЭКИБ.Риск-ассистент AI</t>
         </is>
       </c>
-      <c r="C49" s="9" t="n"/>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="E49" s="9" t="n"/>
-      <c r="F49" s="10" t="n"/>
-      <c r="G49" s="9" t="n"/>
-      <c r="H49" s="8" t="inlineStr">
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="22" t="n"/>
+      <c r="G49" s="11" t="n"/>
+      <c r="H49" s="24" t="inlineStr">
         <is>
           <t>аналитика</t>
         </is>
       </c>
-      <c r="I49" s="9" t="n"/>
-      <c r="J49" s="9" t="n"/>
-      <c r="K49" s="9" t="n"/>
-      <c r="L49" s="9" t="n"/>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="9" t="n"/>
-      <c r="O49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
-      <c r="Q49" s="9" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="11" t="n"/>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="12" t="n"/>
+      <c r="N49" s="11" t="n"/>
+      <c r="O49" s="11" t="n"/>
+      <c r="P49" s="11" t="n"/>
+      <c r="Q49" s="12" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
-      <c r="A50" s="11" t="n"/>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>Рим: Deployment ДА (SberApi); архдефект API-REST-17-5 (3 чд)</t>
         </is>
       </c>
-      <c r="C50" s="9" t="n"/>
-      <c r="D50" s="12" t="inlineStr">
+      <c r="C50" s="16" t="n"/>
+      <c r="D50" s="21" t="inlineStr">
         <is>
           <t>SberApi</t>
         </is>
       </c>
-      <c r="E50" s="12" t="inlineStr">
+      <c r="E50" s="21" t="inlineStr">
         <is>
           <t>архдефект</t>
         </is>
       </c>
-      <c r="F50" s="10" t="n"/>
-      <c r="G50" s="9" t="n"/>
-      <c r="H50" s="9" t="n"/>
-      <c r="I50" s="9" t="n"/>
-      <c r="J50" s="9" t="n"/>
-      <c r="K50" s="9" t="n"/>
-      <c r="L50" s="9" t="n"/>
-      <c r="M50" s="9" t="n"/>
-      <c r="N50" s="9" t="n"/>
-      <c r="O50" s="9" t="n"/>
-      <c r="P50" s="9" t="n"/>
-      <c r="Q50" s="9" t="n"/>
+      <c r="F50" s="22" t="n"/>
+      <c r="G50" s="11" t="n"/>
+      <c r="H50" s="11" t="n"/>
+      <c r="I50" s="11" t="n"/>
+      <c r="J50" s="11" t="n"/>
+      <c r="K50" s="11" t="n"/>
+      <c r="L50" s="11" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="11" t="n"/>
+      <c r="O50" s="11" t="n"/>
+      <c r="P50" s="11" t="n"/>
+      <c r="Q50" s="12" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="11" t="n"/>
-      <c r="B51" s="7" t="inlineStr">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>Рим: Сделки_ДЗО — выход на КО</t>
         </is>
       </c>
-      <c r="C51" s="9" t="n"/>
-      <c r="D51" s="9" t="n"/>
-      <c r="E51" s="9" t="n"/>
-      <c r="F51" s="10" t="n"/>
-      <c r="G51" s="9" t="n"/>
-      <c r="H51" s="9" t="n"/>
-      <c r="I51" s="9" t="n"/>
-      <c r="J51" s="17" t="inlineStr">
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="11" t="n"/>
+      <c r="E51" s="11" t="n"/>
+      <c r="F51" s="22" t="n"/>
+      <c r="G51" s="11" t="n"/>
+      <c r="H51" s="11" t="n"/>
+      <c r="I51" s="11" t="n"/>
+      <c r="J51" s="28" t="inlineStr">
         <is>
           <t>◇ Выход на КО по сделкам</t>
         </is>
       </c>
-      <c r="K51" s="9" t="n"/>
-      <c r="L51" s="9" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
-      <c r="O51" s="9" t="n"/>
-      <c r="P51" s="9" t="n"/>
-      <c r="Q51" s="9" t="n"/>
+      <c r="K51" s="11" t="n"/>
+      <c r="L51" s="11" t="n"/>
+      <c r="M51" s="12" t="n"/>
+      <c r="N51" s="11" t="n"/>
+      <c r="O51" s="11" t="n"/>
+      <c r="P51" s="11" t="n"/>
+      <c r="Q51" s="12" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="11" t="n"/>
-      <c r="B52" s="7" t="inlineStr">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>Рим: Сделки_ДЗО — утилизация сделок с ПАЛ/ИР</t>
         </is>
       </c>
-      <c r="C52" s="9" t="n"/>
-      <c r="D52" s="9" t="n"/>
-      <c r="E52" s="9" t="n"/>
-      <c r="F52" s="10" t="n"/>
-      <c r="G52" s="9" t="n"/>
-      <c r="H52" s="9" t="n"/>
-      <c r="I52" s="9" t="n"/>
-      <c r="J52" s="9" t="n"/>
-      <c r="K52" s="12" t="inlineStr">
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="11" t="n"/>
+      <c r="E52" s="11" t="n"/>
+      <c r="F52" s="22" t="n"/>
+      <c r="G52" s="11" t="n"/>
+      <c r="H52" s="11" t="n"/>
+      <c r="I52" s="11" t="n"/>
+      <c r="J52" s="11" t="n"/>
+      <c r="K52" s="21" t="inlineStr">
         <is>
           <t>ПАЛ/ИР</t>
         </is>
       </c>
-      <c r="L52" s="9" t="n"/>
-      <c r="M52" s="9" t="n"/>
-      <c r="N52" s="9" t="n"/>
-      <c r="O52" s="9" t="n"/>
-      <c r="P52" s="9" t="n"/>
-      <c r="Q52" s="9" t="n"/>
+      <c r="L52" s="11" t="n"/>
+      <c r="M52" s="12" t="n"/>
+      <c r="N52" s="11" t="n"/>
+      <c r="O52" s="11" t="n"/>
+      <c r="P52" s="11" t="n"/>
+      <c r="Q52" s="12" t="n"/>
     </row>
     <row r="53" ht="22" customHeight="1">
-      <c r="A53" s="11" t="n"/>
-      <c r="B53" s="7" t="inlineStr">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>Даша: откл. РЭКИБ.Flow (3 ч/д); дефолтная реструктуризация (4 чд); скрытие (5 чд)</t>
         </is>
       </c>
-      <c r="C53" s="12" t="inlineStr">
+      <c r="C53" s="14" t="inlineStr">
         <is>
           <t>Flow</t>
         </is>
       </c>
-      <c r="D53" s="12" t="inlineStr">
+      <c r="D53" s="21" t="inlineStr">
         <is>
           <t>рестр.</t>
         </is>
       </c>
-      <c r="E53" s="12" t="inlineStr">
+      <c r="E53" s="21" t="inlineStr">
         <is>
           <t>скрытие</t>
         </is>
       </c>
-      <c r="F53" s="10" t="n"/>
-      <c r="G53" s="9" t="n"/>
-      <c r="H53" s="9" t="n"/>
-      <c r="I53" s="9" t="n"/>
-      <c r="J53" s="9" t="n"/>
-      <c r="K53" s="9" t="n"/>
-      <c r="L53" s="9" t="n"/>
-      <c r="M53" s="9" t="n"/>
-      <c r="N53" s="9" t="n"/>
-      <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
-      <c r="Q53" s="9" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="11" t="n"/>
+      <c r="H53" s="11" t="n"/>
+      <c r="I53" s="11" t="n"/>
+      <c r="J53" s="11" t="n"/>
+      <c r="K53" s="11" t="n"/>
+      <c r="L53" s="11" t="n"/>
+      <c r="M53" s="12" t="n"/>
+      <c r="N53" s="11" t="n"/>
+      <c r="O53" s="11" t="n"/>
+      <c r="P53" s="11" t="n"/>
+      <c r="Q53" s="12" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="11" t="n"/>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>Максим: таймауты REST + дестр. тест (4 чд); ретро-анализ кластера (5 чд)</t>
         </is>
       </c>
-      <c r="C54" s="12" t="inlineStr">
+      <c r="C54" s="14" t="inlineStr">
         <is>
           <t>REST</t>
         </is>
       </c>
-      <c r="D54" s="12" t="inlineStr">
+      <c r="D54" s="21" t="inlineStr">
         <is>
           <t>ретро</t>
         </is>
       </c>
-      <c r="E54" s="9" t="n"/>
-      <c r="F54" s="10" t="n"/>
-      <c r="G54" s="9" t="n"/>
-      <c r="H54" s="9" t="n"/>
-      <c r="I54" s="9" t="n"/>
-      <c r="J54" s="9" t="n"/>
-      <c r="K54" s="9" t="n"/>
-      <c r="L54" s="9" t="n"/>
-      <c r="M54" s="9" t="n"/>
-      <c r="N54" s="9" t="n"/>
-      <c r="O54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="Q54" s="9" t="n"/>
+      <c r="E54" s="11" t="n"/>
+      <c r="F54" s="22" t="n"/>
+      <c r="G54" s="11" t="n"/>
+      <c r="H54" s="11" t="n"/>
+      <c r="I54" s="11" t="n"/>
+      <c r="J54" s="11" t="n"/>
+      <c r="K54" s="11" t="n"/>
+      <c r="L54" s="11" t="n"/>
+      <c r="M54" s="12" t="n"/>
+      <c r="N54" s="11" t="n"/>
+      <c r="O54" s="11" t="n"/>
+      <c r="P54" s="11" t="n"/>
+      <c r="Q54" s="12" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="11" t="n"/>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="9" t="inlineStr">
         <is>
           <t>Миша: SDD+скилл; комплектность НЭР; БИТЛ/Кафка/DropAPP; пакетная загрузка</t>
         </is>
       </c>
-      <c r="C55" s="12" t="inlineStr">
+      <c r="C55" s="14" t="inlineStr">
         <is>
           <t>SDD</t>
         </is>
       </c>
-      <c r="D55" s="12" t="inlineStr">
+      <c r="D55" s="21" t="inlineStr">
         <is>
           <t>НЭР</t>
         </is>
       </c>
-      <c r="E55" s="12" t="inlineStr">
+      <c r="E55" s="21" t="inlineStr">
         <is>
           <t>БИТЛ</t>
         </is>
       </c>
-      <c r="F55" s="14" t="inlineStr">
+      <c r="F55" s="29" t="inlineStr">
         <is>
           <t>пакетная</t>
         </is>
       </c>
-      <c r="G55" s="9" t="n"/>
-      <c r="H55" s="9" t="n"/>
-      <c r="I55" s="9" t="n"/>
-      <c r="J55" s="9" t="n"/>
-      <c r="K55" s="9" t="n"/>
-      <c r="L55" s="9" t="n"/>
-      <c r="M55" s="9" t="n"/>
-      <c r="N55" s="9" t="n"/>
-      <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="n"/>
-      <c r="Q55" s="9" t="n"/>
+      <c r="G55" s="11" t="n"/>
+      <c r="H55" s="11" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="11" t="n"/>
+      <c r="K55" s="11" t="n"/>
+      <c r="L55" s="11" t="n"/>
+      <c r="M55" s="12" t="n"/>
+      <c r="N55" s="11" t="n"/>
+      <c r="O55" s="11" t="n"/>
+      <c r="P55" s="11" t="n"/>
+      <c r="Q55" s="12" t="n"/>
     </row>
     <row r="58">
-      <c r="B58" s="19" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>Легенда:</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="20" t="inlineStr">
+      <c r="B59" s="31" t="inlineStr">
         <is>
           <t>◆ выполнено / факт</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="21" t="inlineStr">
+      <c r="B60" s="32" t="inlineStr">
         <is>
           <t>◇ план / под вопросом</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="22" t="inlineStr">
+      <c r="B61" s="33" t="inlineStr">
         <is>
           <t>работы (разработка)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="23" t="inlineStr">
+      <c r="B62" s="34" t="inlineStr">
         <is>
           <t>аналитика (SDD)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="24" t="inlineStr">
+      <c r="B63" s="35" t="inlineStr">
+        <is>
+          <t>тестирование</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="36" t="inlineStr">
         <is>
           <t>оценка т/з</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="B64" s="25" t="inlineStr">
+    <row r="65">
+      <c r="B65" s="37" t="inlineStr">
         <is>
           <t>отпуск</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="38" t="inlineStr">
+        <is>
+          <t>⚑ старт</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="39" t="inlineStr">
+        <is>
+          <t>⚑ финиш</t>
         </is>
       </c>
     </row>
